--- a/branches/fix/ig-level-po-catalogue/ValueSet-mii-vs-dokument-format-code.xlsx
+++ b/branches/fix/ig-level-po-catalogue/ValueSet-mii-vs-dokument-format-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T19:59:45+00:00</t>
+    <t>2026-08-05T20:43:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
